--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="179">
   <si>
     <t>Sezione</t>
   </si>
@@ -50,7 +50,7 @@
     <t>Sentenza straniera</t>
   </si>
   <si>
-    <t>Nota di trasmissione da parte dell’autorità consolare o diplomatica</t>
+    <t>Nota di trasmissione da parte dell'autorità consolare o diplomatica</t>
   </si>
   <si>
     <t>Formula</t>
@@ -110,211 +110,241 @@
     <t>cognome</t>
   </si>
   <si>
+    <t>evento.flagOmogenitoriale,=,true</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>Identificativo unico nazionale</t>
+  </si>
+  <si>
+    <t>idANPR</t>
+  </si>
+  <si>
+    <t>Sesso</t>
+  </si>
+  <si>
+    <t>sesso</t>
+  </si>
+  <si>
+    <t>Formato Data Nascita</t>
+  </si>
+  <si>
+    <t>idFormatodata</t>
+  </si>
+  <si>
+    <t>Formato Data Nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>formatodata</t>
+  </si>
+  <si>
+    <t>Data nascita</t>
+  </si>
+  <si>
+    <t>dataNascita</t>
+  </si>
+  <si>
+    <t>Stato di nascita</t>
+  </si>
+  <si>
+    <t>idStatoNascita</t>
+  </si>
+  <si>
+    <t>Stato di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeStatoNascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita</t>
+  </si>
+  <si>
+    <t>idProvinciaNascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaNascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita</t>
+  </si>
+  <si>
+    <t>idComuneNascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneNascita</t>
+  </si>
+  <si>
+    <t>Località estera</t>
+  </si>
+  <si>
+    <t>localitaEsteraNascita</t>
+  </si>
+  <si>
+    <t>Nazionalità</t>
+  </si>
+  <si>
+    <t>idNazionalita</t>
+  </si>
+  <si>
+    <t>Nazionalità - Descrizione</t>
+  </si>
+  <si>
+    <t>nazionalita</t>
+  </si>
+  <si>
+    <t>Comprensione</t>
+  </si>
+  <si>
+    <t>tipoImpedimento</t>
+  </si>
+  <si>
+    <t>Residenza non nota</t>
+  </si>
+  <si>
+    <t>flagIrreperibile</t>
+  </si>
+  <si>
+    <t>Stato di residenza</t>
+  </si>
+  <si>
+    <t>idStatoResidenza</t>
+  </si>
+  <si>
+    <t>Stato di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeStatoResidenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza</t>
+  </si>
+  <si>
+    <t>idProvinciaResidenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaResidenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza</t>
+  </si>
+  <si>
+    <t>idComuneResidenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneResidenza</t>
+  </si>
+  <si>
+    <t>Indirizzo di residenza</t>
+  </si>
+  <si>
+    <t>indirizzoResidenza</t>
+  </si>
+  <si>
+    <t>flag dichiarante</t>
+  </si>
+  <si>
+    <t>flagDichiarante</t>
+  </si>
+  <si>
+    <t>flag comparente</t>
+  </si>
+  <si>
+    <t>flagComparente</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
+  </si>
+  <si>
+    <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Provincia AIRE</t>
+  </si>
+  <si>
+    <t>idProvinciaAIRE</t>
+  </si>
+  <si>
+    <t>Provincia AIRE - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaAIRE</t>
+  </si>
+  <si>
+    <t>Comune AIRE</t>
+  </si>
+  <si>
+    <t>idComuneAIRE</t>
+  </si>
+  <si>
+    <t>Comune AIRE - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Genitore</t>
+  </si>
+  <si>
+    <t>evento.flagOmogenitoriale,=,false</t>
+  </si>
+  <si>
+    <t>Madre</t>
+  </si>
+  <si>
+    <t>evento.madre</t>
+  </si>
+  <si>
+    <t>Intestatario</t>
+  </si>
+  <si>
+    <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
+  </si>
+  <si>
+    <t>Madre biologica</t>
+  </si>
+  <si>
+    <t>evento.madreBiologica</t>
+  </si>
+  <si>
     <t>opzionale</t>
   </si>
   <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>nome</t>
-  </si>
-  <si>
-    <t>Identificativo unico nazionale</t>
-  </si>
-  <si>
-    <t>idANPR</t>
-  </si>
-  <si>
-    <t>Sesso</t>
-  </si>
-  <si>
-    <t>sesso</t>
-  </si>
-  <si>
-    <t>Formato Data Nascita</t>
-  </si>
-  <si>
-    <t>idFormatodata</t>
-  </si>
-  <si>
-    <t>Formato Data Nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>formatodata</t>
-  </si>
-  <si>
-    <t>Data nascita</t>
-  </si>
-  <si>
-    <t>dataNascita</t>
-  </si>
-  <si>
-    <t>Stato di nascita</t>
-  </si>
-  <si>
-    <t>idStatoNascita</t>
-  </si>
-  <si>
-    <t>Stato di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeStatoNascita</t>
-  </si>
-  <si>
-    <t>Provincia di nascita</t>
-  </si>
-  <si>
-    <t>idProvinciaNascita</t>
-  </si>
-  <si>
-    <t>Provincia di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaNascita</t>
-  </si>
-  <si>
-    <t>Comune di nascita</t>
-  </si>
-  <si>
-    <t>idComuneNascita</t>
-  </si>
-  <si>
-    <t>Comune di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneNascita</t>
-  </si>
-  <si>
-    <t>Località estera</t>
-  </si>
-  <si>
-    <t>localitaEsteraNascita</t>
-  </si>
-  <si>
-    <t>Nazionalità</t>
-  </si>
-  <si>
-    <t>idNazionalita</t>
-  </si>
-  <si>
-    <t>Nazionalità - Descrizione</t>
-  </si>
-  <si>
-    <t>nazionalita</t>
-  </si>
-  <si>
-    <t>Comprensione</t>
-  </si>
-  <si>
-    <t>tipoImpedimento</t>
-  </si>
-  <si>
-    <t>Residenza non nota</t>
-  </si>
-  <si>
-    <t>flagIrreperibile</t>
-  </si>
-  <si>
-    <t>Stato di residenza</t>
-  </si>
-  <si>
-    <t>idStatoResidenza</t>
-  </si>
-  <si>
-    <t>Stato di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeStatoResidenza</t>
-  </si>
-  <si>
-    <t>Provincia di residenza</t>
-  </si>
-  <si>
-    <t>idProvinciaResidenza</t>
-  </si>
-  <si>
-    <t>Provincia di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaResidenza</t>
-  </si>
-  <si>
-    <t>Comune di residenza</t>
-  </si>
-  <si>
-    <t>idComuneResidenza</t>
-  </si>
-  <si>
-    <t>Comune di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneResidenza</t>
-  </si>
-  <si>
-    <t>Indirizzo di residenza</t>
-  </si>
-  <si>
-    <t>indirizzoResidenza</t>
-  </si>
-  <si>
-    <t>flag dichiarante</t>
-  </si>
-  <si>
-    <t>flagDichiarante</t>
-  </si>
-  <si>
-    <t>flag comparente</t>
-  </si>
-  <si>
-    <t>flagComparente</t>
-  </si>
-  <si>
-    <t>Firmatario</t>
-  </si>
-  <si>
-    <t>flagFirmatario</t>
-  </si>
-  <si>
-    <t>Provincia AIRE</t>
-  </si>
-  <si>
-    <t>idProvinciaAIRE</t>
-  </si>
-  <si>
-    <t>Provincia AIRE - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaAIRE</t>
-  </si>
-  <si>
-    <t>Comune AIRE</t>
-  </si>
-  <si>
-    <t>idComuneAIRE</t>
-  </si>
-  <si>
-    <t>Comune AIRE - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneAIRE</t>
-  </si>
-  <si>
-    <t>Madre</t>
-  </si>
-  <si>
-    <t>evento.madre</t>
-  </si>
-  <si>
-    <t>Intestatario</t>
-  </si>
-  <si>
-    <t>evento.intestatari[0]</t>
-  </si>
-  <si>
-    <t>Residenza al momento dell'evento originario</t>
-  </si>
-  <si>
-    <t>residenzaOriginaria</t>
+    <t>flag firmatario</t>
+  </si>
+  <si>
+    <t>Trasmissione residenza estera</t>
+  </si>
+  <si>
+    <t>flagTrasmissioneResidenzaEstera</t>
+  </si>
+  <si>
+    <t>Padre biologico</t>
+  </si>
+  <si>
+    <t>evento.padreBiologico</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -510,6 +540,15 @@
   </si>
   <si>
     <t>testoLibero</t>
+  </si>
+  <si>
+    <t>Dettagli evento</t>
+  </si>
+  <si>
+    <t>Adozione omogenitoriale</t>
+  </si>
+  <si>
+    <t>flagOmogenitoriale</t>
   </si>
 </sst>
 </file>
@@ -568,16 +607,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="60.6640625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.05859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="31.45703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1557,7 +1596,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>31</v>
@@ -1566,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44">
@@ -1580,7 +1619,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>34</v>
@@ -1589,7 +1628,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45">
@@ -1603,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>36</v>
@@ -1612,7 +1651,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46">
@@ -1626,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>38</v>
@@ -1635,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
@@ -1649,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>40</v>
@@ -1658,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
@@ -1672,7 +1711,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>42</v>
@@ -1681,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49">
@@ -1695,7 +1734,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>44</v>
@@ -1704,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
@@ -1718,7 +1757,7 @@
         <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>46</v>
@@ -1727,7 +1766,7 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51">
@@ -1741,7 +1780,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>48</v>
@@ -1750,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
@@ -1764,7 +1803,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>50</v>
@@ -1773,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53">
@@ -1787,7 +1826,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>52</v>
@@ -1796,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54">
@@ -1810,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>54</v>
@@ -1819,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55">
@@ -1833,7 +1872,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>56</v>
@@ -1842,7 +1881,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
@@ -1856,7 +1895,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>58</v>
@@ -1865,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57">
@@ -1879,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>60</v>
@@ -1888,7 +1927,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58">
@@ -1902,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -1911,7 +1950,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59">
@@ -1925,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>64</v>
@@ -1934,7 +1973,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60">
@@ -1948,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>66</v>
@@ -1957,7 +1996,7 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61">
@@ -1971,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>68</v>
@@ -1980,7 +2019,7 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62">
@@ -1994,7 +2033,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>70</v>
@@ -2003,7 +2042,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63">
@@ -2017,7 +2056,7 @@
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>72</v>
@@ -2026,7 +2065,7 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64">
@@ -2040,7 +2079,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>74</v>
@@ -2049,7 +2088,7 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65">
@@ -2063,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>76</v>
@@ -2072,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66">
@@ -2086,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>78</v>
@@ -2095,7 +2134,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67">
@@ -2109,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>80</v>
@@ -2118,7 +2157,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68">
@@ -2132,7 +2171,7 @@
         <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>82</v>
@@ -2141,7 +2180,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69">
@@ -2155,7 +2194,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>84</v>
@@ -2164,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70">
@@ -2178,7 +2217,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>86</v>
@@ -2187,7 +2226,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71">
@@ -2201,7 +2240,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>88</v>
@@ -2210,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72">
@@ -2224,7 +2263,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>90</v>
@@ -2233,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73">
@@ -2247,7 +2286,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>92</v>
@@ -2256,7 +2295,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74">
@@ -2270,7 +2309,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>94</v>
@@ -2279,7 +2318,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75">
@@ -2302,7 +2341,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76">
@@ -2325,7 +2364,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
@@ -2348,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
@@ -2371,7 +2410,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -2394,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80">
@@ -2417,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -2440,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
@@ -2463,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -2486,7 +2525,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -2509,7 +2548,7 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
@@ -2532,7 +2571,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86">
@@ -2555,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -2578,7 +2617,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -2601,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89">
@@ -2624,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
@@ -2647,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
@@ -2670,7 +2709,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92">
@@ -2693,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93">
@@ -2716,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94">
@@ -2739,7 +2778,7 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
@@ -2762,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
@@ -2785,7 +2824,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97">
@@ -2808,7 +2847,7 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98">
@@ -2831,7 +2870,7 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99">
@@ -2854,7 +2893,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -2877,7 +2916,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101">
@@ -2900,7 +2939,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102">
@@ -2911,7 +2950,7 @@
         <v>85</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>98</v>
@@ -2923,7 +2962,7 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103">
@@ -2946,7 +2985,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104">
@@ -2969,7 +3008,7 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
@@ -2992,7 +3031,7 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106">
@@ -3015,760 +3054,760 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
@@ -3779,19 +3818,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3802,19 +3841,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -3825,19 +3864,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -3848,19 +3887,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
@@ -3871,19 +3910,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>161</v>
+        <v>42</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
@@ -3894,19 +3933,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
@@ -3917,24 +3956,3037 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="C262" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E146" s="2" t="s">
+      <c r="C272" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G146" s="2" t="s">
+      <c r="F272" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G277" s="2" t="s">
         <v>21</v>
       </c>
     </row>
